--- a/data/importation.xlsx
+++ b/data/importation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>Id</t>
   </si>
@@ -55,10 +55,19 @@
     <t>Air</t>
   </si>
   <si>
+    <t>Terrestre</t>
+  </si>
+  <si>
     <t>Douala</t>
   </si>
   <si>
+    <t>Brazzaville</t>
+  </si>
+  <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>Tradex</t>
   </si>
   <si>
     <t>Janvier</t>
@@ -423,7 +432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -475,10 +484,10 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2">
         <v>10000</v>
@@ -499,9 +508,50 @@
         <v>2000</v>
       </c>
       <c r="L2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="M2">
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3">
+        <v>10000</v>
+      </c>
+      <c r="G3">
+        <v>12500</v>
+      </c>
+      <c r="H3">
+        <v>11500</v>
+      </c>
+      <c r="I3">
+        <v>14500</v>
+      </c>
+      <c r="J3" s="2">
+        <v>36526</v>
+      </c>
+      <c r="K3">
+        <v>2000</v>
+      </c>
+      <c r="L3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3">
         <v>1</v>
       </c>
     </row>

--- a/data/importation.xlsx
+++ b/data/importation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>Id</t>
   </si>
@@ -64,10 +64,16 @@
     <t>Brazzaville</t>
   </si>
   <si>
+    <t>Limbe</t>
+  </si>
+  <si>
     <t>Total</t>
   </si>
   <si>
     <t>Tradex</t>
+  </si>
+  <si>
+    <t>Elf</t>
   </si>
   <si>
     <t>Janvier</t>
@@ -432,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -487,7 +493,7 @@
         <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>10000</v>
@@ -508,7 +514,7 @@
         <v>2000</v>
       </c>
       <c r="L2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -528,7 +534,7 @@
         <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3">
         <v>10000</v>
@@ -549,9 +555,50 @@
         <v>2000</v>
       </c>
       <c r="L3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4">
+        <v>7500</v>
+      </c>
+      <c r="G4">
+        <v>6500</v>
+      </c>
+      <c r="H4">
+        <v>4500</v>
+      </c>
+      <c r="I4">
+        <v>9500</v>
+      </c>
+      <c r="J4" s="2">
+        <v>36526</v>
+      </c>
+      <c r="K4">
+        <v>2000</v>
+      </c>
+      <c r="L4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4">
         <v>1</v>
       </c>
     </row>

--- a/data/importation.xlsx
+++ b/data/importation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
   <si>
     <t>Id</t>
   </si>
@@ -77,6 +77,9 @@
   </si>
   <si>
     <t>Janvier</t>
+  </si>
+  <si>
+    <t>Février</t>
   </si>
 </sst>
 </file>
@@ -438,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -602,6 +605,88 @@
         <v>1</v>
       </c>
     </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5">
+        <v>3500</v>
+      </c>
+      <c r="G5">
+        <v>4500</v>
+      </c>
+      <c r="H5">
+        <v>6500</v>
+      </c>
+      <c r="I5">
+        <v>7500</v>
+      </c>
+      <c r="J5" s="2">
+        <v>36892</v>
+      </c>
+      <c r="K5">
+        <v>2001</v>
+      </c>
+      <c r="L5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6">
+        <v>8500</v>
+      </c>
+      <c r="G6">
+        <v>6500</v>
+      </c>
+      <c r="H6">
+        <v>7500</v>
+      </c>
+      <c r="I6">
+        <v>9500</v>
+      </c>
+      <c r="J6" s="2">
+        <v>37288</v>
+      </c>
+      <c r="K6">
+        <v>2002</v>
+      </c>
+      <c r="L6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/importation.xlsx
+++ b/data/importation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="25">
   <si>
     <t>Id</t>
   </si>
@@ -80,6 +80,15 @@
   </si>
   <si>
     <t>Février</t>
+  </si>
+  <si>
+    <t>Juin</t>
+  </si>
+  <si>
+    <t>Aôut</t>
+  </si>
+  <si>
+    <t>Octobre</t>
   </si>
 </sst>
 </file>
@@ -441,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -687,6 +696,129 @@
         <v>2</v>
       </c>
     </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>9800</v>
+      </c>
+      <c r="G7">
+        <v>7500</v>
+      </c>
+      <c r="H7">
+        <v>5600</v>
+      </c>
+      <c r="I7">
+        <v>10500</v>
+      </c>
+      <c r="J7" s="2">
+        <v>37799</v>
+      </c>
+      <c r="K7">
+        <v>2003</v>
+      </c>
+      <c r="L7" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8">
+        <v>10600</v>
+      </c>
+      <c r="G8">
+        <v>8600</v>
+      </c>
+      <c r="H8">
+        <v>9800</v>
+      </c>
+      <c r="I8">
+        <v>10800</v>
+      </c>
+      <c r="J8" s="2">
+        <v>38218</v>
+      </c>
+      <c r="K8">
+        <v>2004</v>
+      </c>
+      <c r="L8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9">
+        <v>15000</v>
+      </c>
+      <c r="G9">
+        <v>17600</v>
+      </c>
+      <c r="H9">
+        <v>10600</v>
+      </c>
+      <c r="I9">
+        <v>18000</v>
+      </c>
+      <c r="J9" s="2">
+        <v>38645</v>
+      </c>
+      <c r="K9">
+        <v>2005</v>
+      </c>
+      <c r="L9" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/importation.xlsx
+++ b/data/importation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
   <si>
     <t>Id</t>
   </si>
@@ -89,6 +89,9 @@
   </si>
   <si>
     <t>Octobre</t>
+  </si>
+  <si>
+    <t>Novembre</t>
   </si>
 </sst>
 </file>
@@ -450,7 +453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -819,6 +822,47 @@
         <v>10</v>
       </c>
     </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10">
+        <v>7500</v>
+      </c>
+      <c r="G10">
+        <v>12500</v>
+      </c>
+      <c r="H10">
+        <v>9450</v>
+      </c>
+      <c r="I10">
+        <v>8250</v>
+      </c>
+      <c r="J10" s="2">
+        <v>39037</v>
+      </c>
+      <c r="K10">
+        <v>2006</v>
+      </c>
+      <c r="L10" t="s">
+        <v>25</v>
+      </c>
+      <c r="M10">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
